--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/bu-04/HRM/post DFS_HRM-2031-0192/Panel-28/Coupon front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU04_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.93077</v>
+        <v>17.15371</v>
       </c>
       <c r="D2" t="n">
-        <v>16.9547</v>
+        <v>16.52297</v>
       </c>
       <c r="E2" t="n">
-        <v>16.79119</v>
+        <v>17.06524</v>
       </c>
       <c r="F2" t="n">
-        <v>43.68019</v>
+        <v>42.48956</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05143</v>
+        <v>0.05083</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86727</v>
+        <v>1.84328</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.81777</v>
+        <v>16.88053</v>
       </c>
       <c r="D3" t="n">
-        <v>16.57086</v>
+        <v>16.52075</v>
       </c>
       <c r="E3" t="n">
-        <v>16.89714</v>
+        <v>16.55491</v>
       </c>
       <c r="F3" t="n">
-        <v>42.15863</v>
+        <v>43.71247</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05073</v>
+        <v>0.05035</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84629</v>
+        <v>1.86545</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.02078</v>
+        <v>17.11578</v>
       </c>
       <c r="D4" t="n">
-        <v>16.69976</v>
+        <v>16.80995</v>
       </c>
       <c r="E4" t="n">
-        <v>16.99438</v>
+        <v>16.87772</v>
       </c>
       <c r="F4" t="n">
-        <v>42.0273</v>
+        <v>43.20405</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05199</v>
+        <v>0.05002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.84328</v>
+        <v>1.87781</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.23617</v>
+        <v>17.29521</v>
       </c>
       <c r="D6" t="n">
-        <v>16.47993</v>
+        <v>16.23451</v>
       </c>
       <c r="E6" t="n">
-        <v>16.51354</v>
+        <v>17.13996</v>
       </c>
       <c r="F6" t="n">
-        <v>21.76494</v>
+        <v>22.1378</v>
       </c>
       <c r="G6" t="n">
-        <v>34.94252</v>
+        <v>34.61857</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.74264</v>
+        <v>16.99729</v>
       </c>
       <c r="D7" t="n">
-        <v>16.19635</v>
+        <v>16.13943</v>
       </c>
       <c r="E7" t="n">
-        <v>16.49075</v>
+        <v>16.44916</v>
       </c>
       <c r="F7" t="n">
-        <v>21.57952</v>
+        <v>21.59751</v>
       </c>
       <c r="G7" t="n">
-        <v>34.30339</v>
+        <v>34.98864</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.90782</v>
+        <v>17.37125</v>
       </c>
       <c r="D8" t="n">
-        <v>16.47581</v>
+        <v>16.28215</v>
       </c>
       <c r="E8" t="n">
-        <v>16.76958</v>
+        <v>16.32403</v>
       </c>
       <c r="F8" t="n">
-        <v>22.22469</v>
+        <v>22.42986</v>
       </c>
       <c r="G8" t="n">
-        <v>35.12661</v>
+        <v>34.4597</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61388</v>
+        <v>0.62362</v>
       </c>
       <c r="D10" t="n">
-        <v>1.14095</v>
+        <v>1.11407</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.60819</v>
+        <v>0.61549</v>
       </c>
       <c r="D11" t="n">
-        <v>1.12851</v>
+        <v>1.11278</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.60722</v>
+        <v>0.61628</v>
       </c>
       <c r="D12" t="n">
-        <v>1.12465</v>
+        <v>1.13499</v>
       </c>
     </row>
   </sheetData>
